--- a/artfynd/A 14565-2020 artfynd.xlsx
+++ b/artfynd/A 14565-2020 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121483314</v>
+        <v>121483315</v>
       </c>
       <c r="B3" t="n">
-        <v>58208</v>
+        <v>58216</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>208242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -841,12 +841,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>äggklumpar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ägg</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121483315</v>
+        <v>121483314</v>
       </c>
       <c r="B4" t="n">
-        <v>58216</v>
+        <v>58208</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,21 +943,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208242</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -967,12 +967,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>äggklumpar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>ägg</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">

--- a/artfynd/A 14565-2020 artfynd.xlsx
+++ b/artfynd/A 14565-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121483321</v>
+        <v>121483323</v>
       </c>
       <c r="B2" t="n">
-        <v>58208</v>
+        <v>58211</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727322</v>
+        <v>727425</v>
       </c>
       <c r="R2" t="n">
-        <v>6628666</v>
+        <v>6628656</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121483315</v>
+        <v>121483314</v>
       </c>
       <c r="B3" t="n">
-        <v>58216</v>
+        <v>58211</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208242</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -841,12 +841,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>äggklumpar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>ägg</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121483314</v>
+        <v>121483321</v>
       </c>
       <c r="B4" t="n">
-        <v>58208</v>
+        <v>58211</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -967,12 +967,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>äggklumpar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ägg</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727437</v>
+        <v>727322</v>
       </c>
       <c r="R4" t="n">
-        <v>6628649</v>
+        <v>6628666</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,10 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121483323</v>
+        <v>121483315</v>
       </c>
       <c r="B5" t="n">
-        <v>58208</v>
+        <v>58219</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,21 +1069,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208249</v>
+        <v>208242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>727425</v>
+        <v>727437</v>
       </c>
       <c r="R5" t="n">
-        <v>6628656</v>
+        <v>6628649</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 14565-2020 artfynd.xlsx
+++ b/artfynd/A 14565-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121483323</v>
+        <v>121483321</v>
       </c>
       <c r="B2" t="n">
         <v>58211</v>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727425</v>
+        <v>727322</v>
       </c>
       <c r="R2" t="n">
-        <v>6628656</v>
+        <v>6628666</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121483314</v>
+        <v>121483316</v>
       </c>
       <c r="B3" t="n">
         <v>58211</v>
@@ -841,12 +841,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>äggklumpar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ägg</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121483321</v>
+        <v>121483315</v>
       </c>
       <c r="B4" t="n">
-        <v>58211</v>
+        <v>58219</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,21 +943,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>208242</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727322</v>
+        <v>727437</v>
       </c>
       <c r="R4" t="n">
-        <v>6628666</v>
+        <v>6628649</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,10 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121483315</v>
+        <v>121483323</v>
       </c>
       <c r="B5" t="n">
-        <v>58219</v>
+        <v>58211</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,21 +1069,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208242</v>
+        <v>208249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>727437</v>
+        <v>727425</v>
       </c>
       <c r="R5" t="n">
-        <v>6628649</v>
+        <v>6628656</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 14565-2020 artfynd.xlsx
+++ b/artfynd/A 14565-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121483321</v>
       </c>
       <c r="B2" t="n">
-        <v>58211</v>
+        <v>58212</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>121483316</v>
       </c>
       <c r="B3" t="n">
-        <v>58211</v>
+        <v>58212</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121483315</v>
+        <v>121483323</v>
       </c>
       <c r="B4" t="n">
-        <v>58219</v>
+        <v>58212</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,21 +943,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208242</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727437</v>
+        <v>727425</v>
       </c>
       <c r="R4" t="n">
-        <v>6628649</v>
+        <v>6628656</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,10 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121483323</v>
+        <v>121483315</v>
       </c>
       <c r="B5" t="n">
-        <v>58211</v>
+        <v>58220</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,21 +1069,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208249</v>
+        <v>208242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>727425</v>
+        <v>727437</v>
       </c>
       <c r="R5" t="n">
-        <v>6628656</v>
+        <v>6628649</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 14565-2020 artfynd.xlsx
+++ b/artfynd/A 14565-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121483321</v>
+        <v>121483316</v>
       </c>
       <c r="B2" t="n">
-        <v>58212</v>
+        <v>58213</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727322</v>
+        <v>727437</v>
       </c>
       <c r="R2" t="n">
-        <v>6628666</v>
+        <v>6628649</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121483316</v>
+        <v>121483323</v>
       </c>
       <c r="B3" t="n">
-        <v>58212</v>
+        <v>58213</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727437</v>
+        <v>727425</v>
       </c>
       <c r="R3" t="n">
-        <v>6628649</v>
+        <v>6628656</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -890,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121483323</v>
+        <v>121483315</v>
       </c>
       <c r="B4" t="n">
-        <v>58212</v>
+        <v>58221</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,21 +943,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>208242</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727425</v>
+        <v>727437</v>
       </c>
       <c r="R4" t="n">
-        <v>6628656</v>
+        <v>6628649</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,10 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121483315</v>
+        <v>121483321</v>
       </c>
       <c r="B5" t="n">
-        <v>58220</v>
+        <v>58213</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,21 +1069,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208242</v>
+        <v>208249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>727437</v>
+        <v>727322</v>
       </c>
       <c r="R5" t="n">
-        <v>6628649</v>
+        <v>6628666</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 14565-2020 artfynd.xlsx
+++ b/artfynd/A 14565-2020 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121483315</v>
+        <v>121483321</v>
       </c>
       <c r="B4" t="n">
-        <v>58221</v>
+        <v>58213</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,21 +943,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208242</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727437</v>
+        <v>727322</v>
       </c>
       <c r="R4" t="n">
-        <v>6628649</v>
+        <v>6628666</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,10 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121483321</v>
+        <v>121483315</v>
       </c>
       <c r="B5" t="n">
-        <v>58213</v>
+        <v>58221</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,21 +1069,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208249</v>
+        <v>208242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>727322</v>
+        <v>727437</v>
       </c>
       <c r="R5" t="n">
-        <v>6628666</v>
+        <v>6628649</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 14565-2020 artfynd.xlsx
+++ b/artfynd/A 14565-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121483316</v>
+        <v>121483321</v>
       </c>
       <c r="B2" t="n">
         <v>58213</v>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727437</v>
+        <v>727322</v>
       </c>
       <c r="R2" t="n">
-        <v>6628649</v>
+        <v>6628666</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121483323</v>
+        <v>121483315</v>
       </c>
       <c r="B3" t="n">
-        <v>58213</v>
+        <v>58221</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>208242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727425</v>
+        <v>727437</v>
       </c>
       <c r="R3" t="n">
-        <v>6628656</v>
+        <v>6628649</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -890,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,7 +927,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121483321</v>
+        <v>121483316</v>
       </c>
       <c r="B4" t="n">
         <v>58213</v>
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727322</v>
+        <v>727437</v>
       </c>
       <c r="R4" t="n">
-        <v>6628666</v>
+        <v>6628649</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,10 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121483315</v>
+        <v>121483323</v>
       </c>
       <c r="B5" t="n">
-        <v>58221</v>
+        <v>58213</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,21 +1069,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208242</v>
+        <v>208249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>727437</v>
+        <v>727425</v>
       </c>
       <c r="R5" t="n">
-        <v>6628649</v>
+        <v>6628656</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 14565-2020 artfynd.xlsx
+++ b/artfynd/A 14565-2020 artfynd.xlsx
@@ -927,7 +927,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121483316</v>
+        <v>121483314</v>
       </c>
       <c r="B4" t="n">
         <v>58213</v>
@@ -967,12 +967,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>äggklumpar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>ägg</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">

--- a/artfynd/A 14565-2020 artfynd.xlsx
+++ b/artfynd/A 14565-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121483321</v>
+        <v>121483316</v>
       </c>
       <c r="B2" t="n">
-        <v>58213</v>
+        <v>58216</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727322</v>
+        <v>727437</v>
       </c>
       <c r="R2" t="n">
-        <v>6628666</v>
+        <v>6628649</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121483315</v>
+        <v>121483323</v>
       </c>
       <c r="B3" t="n">
-        <v>58221</v>
+        <v>58216</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208242</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727437</v>
+        <v>727425</v>
       </c>
       <c r="R3" t="n">
-        <v>6628649</v>
+        <v>6628656</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -890,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121483314</v>
+        <v>121483321</v>
       </c>
       <c r="B4" t="n">
-        <v>58213</v>
+        <v>58216</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -967,12 +967,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>äggklumpar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ägg</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727437</v>
+        <v>727322</v>
       </c>
       <c r="R4" t="n">
-        <v>6628649</v>
+        <v>6628666</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,10 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121483323</v>
+        <v>121483315</v>
       </c>
       <c r="B5" t="n">
-        <v>58213</v>
+        <v>58224</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,21 +1069,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208249</v>
+        <v>208242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>727425</v>
+        <v>727437</v>
       </c>
       <c r="R5" t="n">
-        <v>6628656</v>
+        <v>6628649</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 14565-2020 artfynd.xlsx
+++ b/artfynd/A 14565-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121483315</v>
+        <v>121483323</v>
       </c>
       <c r="B2" t="n">
-        <v>58224</v>
+        <v>58216</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208242</v>
+        <v>208249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727437</v>
+        <v>727425</v>
       </c>
       <c r="R2" t="n">
-        <v>6628649</v>
+        <v>6628656</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121483323</v>
+        <v>121483321</v>
       </c>
       <c r="B3" t="n">
         <v>58216</v>
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727425</v>
+        <v>727322</v>
       </c>
       <c r="R3" t="n">
-        <v>6628656</v>
+        <v>6628666</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -890,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121483321</v>
+        <v>121483315</v>
       </c>
       <c r="B4" t="n">
-        <v>58216</v>
+        <v>58224</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,21 +943,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>208242</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727322</v>
+        <v>727437</v>
       </c>
       <c r="R4" t="n">
-        <v>6628666</v>
+        <v>6628649</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,7 +1053,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121483314</v>
+        <v>121483316</v>
       </c>
       <c r="B5" t="n">
         <v>58216</v>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>äggklumpar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>ägg</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">

--- a/artfynd/A 14565-2020 artfynd.xlsx
+++ b/artfynd/A 14565-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121483323</v>
+        <v>121483321</v>
       </c>
       <c r="B2" t="n">
         <v>58216</v>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727425</v>
+        <v>727322</v>
       </c>
       <c r="R2" t="n">
-        <v>6628656</v>
+        <v>6628666</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121483321</v>
+        <v>121483314</v>
       </c>
       <c r="B3" t="n">
         <v>58216</v>
@@ -841,12 +841,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>äggklumpar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>ägg</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727322</v>
+        <v>727437</v>
       </c>
       <c r="R3" t="n">
-        <v>6628666</v>
+        <v>6628649</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -890,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1053,7 +1053,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121483316</v>
+        <v>121483323</v>
       </c>
       <c r="B5" t="n">
         <v>58216</v>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>727437</v>
+        <v>727425</v>
       </c>
       <c r="R5" t="n">
-        <v>6628649</v>
+        <v>6628656</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
